--- a/Target Folder/QA-Files/zh-CN/Eng Sheet.xlsx
+++ b/Target Folder/QA-Files/zh-CN/Eng Sheet.xlsx
@@ -26,73 +26,73 @@
   <si>
     <r>
       <rPr/>
-      <t>源文本英文 (en-US)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>我愿在骨灰瓮前饮酒，但它奉承着自由意志。在篮球湖中的孩子们的孩子。事实上，对足球的恐惧是房地产的构成。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Mauris mattis sem ex, not easy molestie sapien。tincidunt urn 在 hate receives 的发展，或者 homework trigger course。即使土地很大，也是必要的，它包含了 laoreet quis felis。因此，没有必要治疗这种疾病。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Vestibulum eleifend, ligula from chocolate vehicles, laughter just ultricies ligula, and sometimes lorem from eget ex.Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>我甚至不需要软饮料，还有我的车。我不想过多担心融资。查明这个国家是谁的。直到 Euismod 微笑说没有时间。孩子们现在是谁？这是一种软酱元素。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Hendrerit 放置的船。但篮球只奉承成员。现在，谁是 eros？它也奉承饮料。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Curabitur lacinia cursus diam sed pharetra。看来这位员工很伤心。直到纯粹的仇恨，员工接受了它，航空公司也在其中。我甚至不能携带一个 porta 玻璃容器。每个价格都奉承资产。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>正因为如此，对山谷的恐惧变得柔和。现在，从今以后，哀悼装饰着，也不奉承法庭的喉咙。Aenean 为我喝酒或不喝 Euismod hendrerit。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>一件法衣和一个大箭袋。作为一种妆容，orci 却奉承着喉咙，唇边只有一丝微笑，作为 ligula 临时欢笑的床。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Duis 不是纯粹的 tincidunt。因为谁在欢笑中是明智的？直到山谷房地产的时候。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>我不想买任何卡车，我也不必支付床的价格。这就像我的房地产经纪人一样，让人受宠若惊。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>要成为一名成功的开发者，需要针对目标受众进行定位。批量饮用很容易。在目标床上。</t>
+      <t>源文本 英文 (en-US)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>我愿在骨灰瓮前饮酒，但这却取悦了自由意志。篮球湖中的孩子们的孩子。事实上，对足球的恐惧是房地产的构成。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>毛里斯·马蒂斯前夫，不容易被萨皮恩骚扰。在仇恨中发展出锡卡杜恩，或者家庭作业触发课程。即使土地很大，也需要并且它占据着，拉奥雷特·奎斯·费利斯。因此，没有必要治疗这种疾病。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>前庭电梯，来自巧克力车的韧带，只是乌尔特里西斯韧带的笑声，有时还有埃格特前任的劳伦。杜伊斯·迪格尼西姆·拉库斯·维塔·维尔特·拉奥雷特，维塔·因维斯特拉特·维尔特·阿利奎特。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>我甚至不需要软饮料和我的车。我不想过多担心融资问题。找出这个国家是谁。直到那时才说尤斯莫德的笑容不合时宜。现在的孩子是谁？这是一种软酱料元素。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>亨德雷里特放置的船。但篮球只讨好成员。现在，谁是爱神？它也取悦了饮料。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>库拉比图尔·拉西尼亚·库苏斯·迪亚姆·塞德·法雷特拉。看来员工很难过。直到那是纯粹的仇恨，员工接受了它，航空公司在其中。我甚至不能携带一个便携式动物园。每个价格都取悦了资产。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>正因为如此，对山谷的恐惧变得柔和。现在，从今往后的哀悼装饰，也不取悦法庭的喉咙。Aenean 给我喝，而不是 Euismod hendrerit。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>一件祭服和一个大箭袋。作为妆容，orci 却讨好喉咙，唇边只有一丝微笑，作为韧带暂时欢笑的床。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Duis 不纯粹是 tincidunt。因为谁在欢笑中是明智的？直到山谷房地产的时间。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>我不想买任何卡车，也不必支付床的价格。它就像我的房地产经纪人一样讨人喜欢。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>为了成为一个成功的开发者，需要针对目标受众。大量饮用很容易。在目标床上。</t>
     </r>
   </si>
   <si>
@@ -164,7 +164,7 @@
   <si>
     <r>
       <rPr/>
-      <t>随着人工智能（AI）的兴起，翻译行业正在经历重大变革。从机器翻译系统到先进的神经网络，人工智能正在塑造语言服务的未来。本文探讨了人工智能在翻译行业中不断演变的角色及其在改变工作流程、质量和人类译员角色方面的潜力。</t>
+      <t>随着人工智能（AI）的兴起，翻译行业正在经历重大变革。从机器翻译系统到先进的神经网络，人工智能正在塑造语言服务的未来。本文探讨了人工智能在翻译行业中不断演变的角色及其在改变工作流程、质量和人工译员角色方面的潜力。</t>
     </r>
   </si>
   <si>
@@ -200,7 +200,7 @@
   <si>
     <r>
       <rPr/>
-      <t>人工智能正在通过自然语言处理（NLP）和机器学习等技术重新定义翻译。这些工具有助于理解上下文、语法和句法，从而实现更准确的翻译。人工智能还会从海量数据中学习，并随着时间的推移不断改进。</t>
+      <t>人工智能通过自然语言处理（NLP）和机器学习等技术重新定义了翻译。这些工具有助于理解上下文、语法和句法，从而实现更准确的翻译。人工智能还从海量数据中学习，并随着时间的推移不断改进。</t>
     </r>
   </si>
   <si>
@@ -212,7 +212,7 @@
   <si>
     <r>
       <rPr/>
-      <t>机器翻译（MT）是指使用软件将文本从一种语言翻译成另一种语言。基于人工智能的机器翻译系统可以快速处理大量数据，为翻译任务提供经济高效的解决方案。谷歌翻译、DeepL 和微软翻译是一些主要示例。</t>
+      <t>机器翻译（MT）是指使用软件将文本从一种语言翻译成另一种语言。基于人工智能的机器翻译系统可以快速处理大量数据，为翻译任务提供经济高效的解决方案。谷歌翻译、DeepL和微软翻译是一些领先的例子。</t>
     </r>
   </si>
   <si>
@@ -278,73 +278,73 @@
   <si>
     <r>
       <rPr/>
-      <t>源文本英文 (en-US)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>我愿在骨灰瓮前饮酒，但它奉承着自由意志。在篮球湖中的孩子们的孩子。事实上，对足球的恐惧是房地产的构成。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Mauris mattis sem ex, not easy molestie sapien。tincidunt urn 在 hate receives 的发展，或者 homework trigger course。即使土地很大，也是必要的，它包含了 laoreet quis felis。因此，没有必要治疗这种疾病。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Vestibulum eleifend, ligula from chocolate vehicles, laughter just ultricies ligula, and sometimes lorem from eget ex.Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>我甚至不需要软饮料，还有我的车。我不想过多担心融资。查明这个国家是谁的。直到 Euismod 微笑说没有时间。孩子们现在是谁？这是一种软酱元素。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Hendrerit 放置的船。但篮球只奉承成员。现在，谁是 eros？它也奉承饮料。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Curabitur lacinia cursus diam sed pharetra。看来这位员工很伤心。直到纯粹的仇恨，员工接受了它，航空公司也在其中。我甚至不能携带一个 porta 玻璃容器。每个价格都奉承资产。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>正因为如此，对山谷的恐惧变得柔和。现在，从今以后，哀悼装饰着，也不奉承法庭的喉咙。Aenean 为我喝酒或不喝 Euismod hendrerit。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>一件法衣和一个大箭袋。作为一种妆容，orci 却奉承着喉咙，唇边只有一丝微笑，作为 ligula 临时欢笑的床。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Duis 不是纯粹的 tincidunt。因为谁在欢笑中是明智的？直到山谷房地产的时候。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>我不想买任何卡车，我也不必支付床的价格。这就像我的房地产经纪人一样，让人受宠若惊。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>要成为一名成功的开发者，需要针对目标受众进行定位。批量饮用很容易。在目标床上。</t>
+      <t>源文本 英文 (en-US)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>我愿在骨灰瓮前饮酒，但这却取悦了自由意志。篮球湖中的孩子们的孩子。事实上，对足球的恐惧是房地产的构成。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>毛里斯·马蒂斯前夫，不容易被萨皮恩骚扰。在仇恨中发展出锡卡杜恩，或者家庭作业触发课程。即使土地很大，也需要并且它占据着，拉奥雷特·奎斯·费利斯。因此，没有必要治疗这种疾病。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>前庭电梯，来自巧克力车的韧带，只是乌尔特里西斯韧带的笑声，有时还有埃格特前任的劳伦。杜伊斯·迪格尼西姆·拉库斯·维塔·维尔特·拉奥雷特，维塔·因维斯特拉特·维尔特·阿利奎特。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>我甚至不需要软饮料和我的车。我不想过多担心融资问题。找出这个国家是谁。直到那时才说尤斯莫德的笑容不合时宜。现在的孩子是谁？这是一种软酱料元素。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>亨德雷里特放置的船。但篮球只讨好成员。现在，谁是爱神？它也取悦了饮料。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>库拉比图尔·拉西尼亚·库苏斯·迪亚姆·塞德·法雷特拉。看来员工很难过。直到那是纯粹的仇恨，员工接受了它，航空公司在其中。我甚至不能携带一个便携式动物园。每个价格都取悦了资产。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>正因为如此，对山谷的恐惧变得柔和。现在，从今往后的哀悼装饰，也不取悦法庭的喉咙。Aenean 给我喝，而不是 Euismod hendrerit。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>一件祭服和一个大箭袋。作为妆容，orci 却讨好喉咙，唇边只有一丝微笑，作为韧带暂时欢笑的床。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Duis 不纯粹是 tincidunt。因为谁在欢笑中是明智的？直到山谷房地产的时间。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>我不想买任何卡车，也不必支付床的价格。它就像我的房地产经纪人一样讨人喜欢。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>为了成为一个成功的开发者，需要针对目标受众。大量饮用很容易。在目标床上。</t>
     </r>
   </si>
   <si>
@@ -356,7 +356,7 @@
   <si>
     <r>
       <rPr/>
-      <t>随着人工智能（AI）的兴起，翻译行业正在经历重大变革。从机器翻译系统到先进的神经网络，人工智能正在塑造语言服务的未来。本文探讨了人工智能在翻译行业中不断演变的角色及其在改变工作流程、质量和人类译员角色方面的潜力。</t>
+      <t>随着人工智能（AI）的兴起，翻译行业正在经历重大变革。从机器翻译系统到先进的神经网络，人工智能正在塑造语言服务的未来。本文探讨了人工智能在翻译行业中不断演变的角色及其在改变工作流程、质量和人工译员角色方面的潜力。</t>
     </r>
   </si>
   <si>
@@ -392,7 +392,7 @@
   <si>
     <r>
       <rPr/>
-      <t>人工智能正在通过自然语言处理（NLP）和机器学习等技术重新定义翻译。这些工具有助于理解上下文、语法和句法，从而实现更准确的翻译。人工智能还会从海量数据中学习，并随着时间的推移不断改进。</t>
+      <t>人工智能通过自然语言处理（NLP）和机器学习等技术重新定义了翻译。这些工具有助于理解上下文、语法和句法，从而实现更准确的翻译。人工智能还从海量数据中学习，并随着时间的推移不断改进。</t>
     </r>
   </si>
   <si>
@@ -404,7 +404,7 @@
   <si>
     <r>
       <rPr/>
-      <t>机器翻译（MT）是指使用软件将文本从一种语言翻译成另一种语言。基于人工智能的机器翻译系统可以快速处理大量数据，为翻译任务提供经济高效的解决方案。谷歌翻译、DeepL 和微软翻译是一些主要示例。</t>
+      <t>机器翻译（MT）是指使用软件将文本从一种语言翻译成另一种语言。基于人工智能的机器翻译系统可以快速处理大量数据，为翻译任务提供经济高效的解决方案。谷歌翻译、DeepL和微软翻译是一些领先的例子。</t>
     </r>
   </si>
 </sst>
